--- a/raw_csv_quiz/Quiz_Week02.xlsx
+++ b/raw_csv_quiz/Quiz_Week02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LearningHub\ai-2y-journey\06-other\flashcard-app\raw_csv_quiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{790B6CC9-48EF-4FD8-AF49-F24BEC241F7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BCF45A6-B941-4C74-BBCD-222371C308C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1978" uniqueCount="1241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1988" uniqueCount="1251">
   <si>
     <t>Question</t>
   </si>
@@ -3794,6 +3794,68 @@
   </si>
   <si>
     <t>S3 is</t>
+  </si>
+  <si>
+    <t>The "Lazy Loading" Problem: When you create an EBS volume from a snapshot, AWS makes the volume available to your EC2 instance almost instantly. However, the data isn't actually "on" the volume yet; it's still sitting in Amazon S3.
+The Penalty: When your application tries to read a piece of data for the first time, AWS has to go pull that specific block from S3 and put it on the volume. This causes a delay known as initial read latency or the "first-touch penalty."
+The Solution (FSR): Fast Snapshot Restore (FSR) tells AWS to pre-initialize the blocks. Instead of waiting for you to ask for data, AWS "warms up" the volume immediately. When you attach it to an instance, it delivers 100% performance right out of the box with zero latency.</t>
+  </si>
+  <si>
+    <t>Standard Restore: Like a frozen pizza. You have the pizza (the volume), but you can't eat it (access data) until you've spent time heating up each slice individually. The first bite is slow/cold.
+Fast Snapshot Restore (FSR): Like a pizza delivery. When it arrives, it is already pre-heated and ready to eat immediately. No waiting!</t>
+  </si>
+  <si>
+    <t>Spot Instances.
+Why is this the answer?
+This question highlights the most important trade-off in EC2 pricing: Cost vs. Availability.
+The "Spare Capacity" Discount: AWS has massive amounts of compute power that isn't always being used. To avoid letting it sit idle, they sell it at a massive discount (up to 90% off On-Demand prices). These are called Spot Instances.
+The Catch (Interruption): The reason they are so cheap is that AWS can "reclaim" them with only a 2-minute warning if they need the capacity back for a customer paying full price.
+The Perfect Match: Your question mentions the workload is "fault-tolerant" and "can be interrupted." This is the "secret code" for Spot Instances. Since the batch job can just pick up where it left off or restart without ruining the final result, you can take advantage of the lowest possible price point in the AWS cloud.</t>
+  </si>
+  <si>
+    <t>Think of EC2 pricing like buying a plane ticket:
+On-Demand: You buy a standard ticket. You are guaranteed a seat.
+Reserved: You buy a "frequent flyer" pass for the whole year. Cheaper per flight, but you're committed to the airline.
+Spot Instances: You buy a "Standby" ticket. It’s incredibly cheap, but if the flight fills up with full-paying passengers, you get kicked off and have to wait for the next one.</t>
+  </si>
+  <si>
+    <t>Throughput Optimized HDD (st1).
+Why is this the answer?
+The key to this question lies in understanding the difference between Throughput and IOPS, and matching them to the correct "storage media" (SSD vs. HDD).
+Throughput vs. IOPS: * Throughput is the speed of data transfer (how many Megabytes per second can move). Big Data systems often deal with large, sequential files where throughput is king.
+IOPS is how many small read/write operations happen per second. Databases need high IOPS.
+HDD for Big Data: Hard Disk Drives (HDD) are significantly cheaper than Solid State Drives (SSD). Since the company needs "high throughput" but not "high IOPS," an HDD is the perfect cost-effective fit.
+st1 vs. sc1: * st1 (Throughput Optimized) is designed specifically for frequently accessed, throughput-intensive workloads like Big Data, Data Warehousing, and Log Processing.
+sc1 (Cold HDD) is even cheaper, but it's meant for data that is rarely accessed (archival).</t>
+  </si>
+  <si>
+    <t>IOPS (SSD): Like a busy city intersection. Lots of small cars (small bits of data) turning in different directions constantly. You need high IOPS to handle the chaos.
+Throughput (HDD): Like a wide-open highway. You have giant semi-trucks (large data blocks) moving in a straight line. You don't need fancy intersections; you just need a wide road to move a lot of volume at once.</t>
+  </si>
+  <si>
+    <t>Gateway Load Balancer (GWLB).
+Why is this the answer?
+This is a more advanced networking question, and the "Route Table Entry" part is the biggest clue.
+The "Middleman" for Security: A Gateway Load Balancer is designed to sit in front of virtual appliances, such as firewalls, intrusion detection systems, or deep packet inspection tools.
+Traffic Interception: Unlike a standard Application Load Balancer (which you reach via a URL) or a Network Load Balancer (which you reach via an IP), the GWLB acts as a bump-in-the-wire.
+The Route Table Connection: To force traffic through a firewall (the virtual appliance), you have to change your VPC Route Table. You tell the Route Table: "Any traffic leaving this subnet must first go to the Gateway Load Balancer Endpoint." 4.  The Endpoint: This is technically achieved through a Gateway Load Balancer Endpoint (GWLBE), which is the specific target you put in your Route Table.</t>
+  </si>
+  <si>
+    <t>ALB/NLB: These are like Receptionists. You go directly to them, and they tell you which room (server) to go to.
+GWLB: This is like a Security Checkpoint at the entrance of a base. You don't choose to go there; the road signs (Route Table) are literally painted to force all cars to pass through the checkpoint before they can enter the rest of the facility.</t>
+  </si>
+  <si>
+    <t>A. Switch the EFS performance mode from General Purpose to Max I/O.
+Why is this the answer?
+Amazon EFS (Elastic File System) offers two performance modes. Understanding when to use each is a classic "Cloud Practitioner" exam topic:
+General Purpose (Default): This is great for most things (web servers, content management). It provides the lowest latency per file operation but has a limit on how many operations (throughput) it can handle at once.
+Max I/O: This is designed for massive scale. When you have "hundreds of instances" (as the question states) all hitting the file system at the same time, the "General Purpose" mode can get bottlenecked.
+The Trade-off: Max I/O can handle much higher levels of aggregate throughput and operations per second, but the trade-off is slightly higher latencies for individual file operations. However, at the scale of hundreds of instances, the total "traffic jam" is cleared, making it the more scalable choice.</t>
+  </si>
+  <si>
+    <t>General Purpose: Think of a small local grocery store with one fast cashier. If you go in alone, you get out instantly. But if 500 people show up at once, the line goes out the door.
+Max I/O: Think of a massive warehouse store (like Costco) with 50 cashiers. Each cashier might be a little slower at scanning, but because there are so many of them, they can process 500 people much faster than the single fast cashier could.
+Key Exam Keyword: Whenever you see "Hundreds of instances," "Big Data," or "Large scale" in an EFS question, look for Max I/O.</t>
   </si>
 </sst>
 </file>
@@ -3840,10 +3902,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4486,7 +4551,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>77</v>
       </c>
@@ -4506,7 +4571,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>81</v>
       </c>
@@ -4526,7 +4591,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>86</v>
       </c>
@@ -4546,7 +4611,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>91</v>
       </c>
@@ -4566,7 +4631,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>96</v>
       </c>
@@ -4586,7 +4651,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>101</v>
       </c>
@@ -4606,7 +4671,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>106</v>
       </c>
@@ -4626,7 +4691,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>111</v>
       </c>
@@ -4646,7 +4711,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>116</v>
       </c>
@@ -4666,7 +4731,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>121</v>
       </c>
@@ -4686,7 +4751,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>126</v>
       </c>
@@ -4705,8 +4770,14 @@
       <c r="F27" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G27" s="3" t="s">
+        <v>1241</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>131</v>
       </c>
@@ -4726,7 +4797,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>135</v>
       </c>
@@ -4746,7 +4817,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>139</v>
       </c>
@@ -4766,7 +4837,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>142</v>
       </c>
@@ -4786,7 +4857,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>147</v>
       </c>
@@ -5126,7 +5197,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>201</v>
       </c>
@@ -5146,7 +5217,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>203</v>
       </c>
@@ -5166,7 +5237,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>206</v>
       </c>
@@ -5186,7 +5257,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>210</v>
       </c>
@@ -5206,7 +5277,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>215</v>
       </c>
@@ -5226,7 +5297,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>220</v>
       </c>
@@ -5246,7 +5317,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>225</v>
       </c>
@@ -5266,7 +5337,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>229</v>
       </c>
@@ -5286,7 +5357,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>233</v>
       </c>
@@ -5306,7 +5377,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>238</v>
       </c>
@@ -5326,7 +5397,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>240</v>
       </c>
@@ -5346,7 +5417,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>243</v>
       </c>
@@ -5366,7 +5437,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>244</v>
       </c>
@@ -5386,7 +5457,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>249</v>
       </c>
@@ -5405,8 +5476,14 @@
       <c r="F62" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G62" s="3" t="s">
+        <v>1245</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>252</v>
       </c>
@@ -5426,7 +5503,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>253</v>
       </c>
@@ -5446,7 +5523,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>258</v>
       </c>
@@ -5466,7 +5543,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>263</v>
       </c>
@@ -5486,7 +5563,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>268</v>
       </c>
@@ -5506,7 +5583,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>273</v>
       </c>
@@ -5526,7 +5603,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>278</v>
       </c>
@@ -5546,7 +5623,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>283</v>
       </c>
@@ -5566,7 +5643,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>285</v>
       </c>
@@ -5586,7 +5663,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>289</v>
       </c>
@@ -5606,7 +5683,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>294</v>
       </c>
@@ -5626,7 +5703,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>299</v>
       </c>
@@ -5646,7 +5723,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>304</v>
       </c>
@@ -5666,7 +5743,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>309</v>
       </c>
@@ -5685,8 +5762,14 @@
       <c r="F76" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G76" s="3" t="s">
+        <v>1243</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>310</v>
       </c>
@@ -5706,7 +5789,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>314</v>
       </c>
@@ -5726,7 +5809,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>319</v>
       </c>
@@ -5746,7 +5829,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>324</v>
       </c>
@@ -5766,7 +5849,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>326</v>
       </c>
@@ -5786,7 +5869,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>331</v>
       </c>
@@ -5806,7 +5889,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>336</v>
       </c>
@@ -5826,7 +5909,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>341</v>
       </c>
@@ -5846,7 +5929,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>345</v>
       </c>
@@ -5866,7 +5949,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>347</v>
       </c>
@@ -5885,8 +5968,14 @@
       <c r="F86" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G86" s="3" t="s">
+        <v>1247</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>348</v>
       </c>
@@ -5906,7 +5995,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>353</v>
       </c>
@@ -5926,7 +6015,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>355</v>
       </c>
@@ -5946,7 +6035,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>360</v>
       </c>
@@ -5966,7 +6055,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>365</v>
       </c>
@@ -5986,7 +6075,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>366</v>
       </c>
@@ -6006,7 +6095,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>367</v>
       </c>
@@ -6026,7 +6115,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>371</v>
       </c>
@@ -6046,7 +6135,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>374</v>
       </c>
@@ -6066,7 +6155,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>377</v>
       </c>
@@ -6726,7 +6815,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>500</v>
       </c>
@@ -6746,7 +6835,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>341</v>
       </c>
@@ -6766,7 +6855,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>506</v>
       </c>
@@ -6786,7 +6875,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>507</v>
       </c>
@@ -6806,7 +6895,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>512</v>
       </c>
@@ -6826,7 +6915,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>514</v>
       </c>
@@ -6846,7 +6935,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>519</v>
       </c>
@@ -6866,7 +6955,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>524</v>
       </c>
@@ -6886,7 +6975,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>529</v>
       </c>
@@ -6905,8 +6994,14 @@
       <c r="F137" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G137" s="3" t="s">
+        <v>1249</v>
+      </c>
+      <c r="H137" s="3" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>534</v>
       </c>
@@ -6926,7 +7021,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>535</v>
       </c>
@@ -6946,7 +7041,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>540</v>
       </c>
@@ -6966,7 +7061,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>545</v>
       </c>
@@ -6986,7 +7081,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>550</v>
       </c>
@@ -7006,7 +7101,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>555</v>
       </c>
@@ -7026,7 +7121,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>560</v>
       </c>
